--- a/配置表格/G怪物刷新配置.xlsx
+++ b/配置表格/G怪物刷新配置.xlsx
@@ -2803,7 +2803,7 @@
         <v>39</v>
       </c>
       <c r="H10" s="11">
-        <v>60021000</v>
+        <v>60011020</v>
       </c>
       <c r="I10" s="12">
         <v>5</v>
